--- a/Experiment analysis results/Additional file 2.xlsx
+++ b/Experiment analysis results/Additional file 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E0A453-8BDF-4280-BE69-956510F2F9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52D1DE6-8C1E-446F-A7BE-AC3301C2AAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>#Reference cells</t>
   </si>
   <si>
-    <t>Cell types</t>
-  </si>
-  <si>
     <t>D4</t>
   </si>
   <si>
@@ -118,6 +115,9 @@
   </si>
   <si>
     <t>#CARD_SCMapping-inferred cells</t>
+  </si>
+  <si>
+    <t>Cell-type abundance</t>
   </si>
 </sst>
 </file>
@@ -257,41 +257,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,82 +597,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="14"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="12"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="R2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>5</v>
@@ -680,13 +680,13 @@
     </row>
     <row r="3" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="2">
         <v>7755</v>
@@ -738,14 +738,14 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>6413</v>
@@ -753,83 +753,83 @@
       <c r="E4" s="1">
         <v>875</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>1964</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>7352</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="13">
         <v>226.365330534717</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="13">
         <v>101.545942057183</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="13">
         <v>60.270814082894198</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="13">
         <v>228.13890517309201</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="13">
         <v>67.248950790620995</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="13">
         <v>183.851668411308</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="13">
         <v>120.27807263202</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="13">
         <v>106.63898980958901</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="13">
         <v>445.95896171367599</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="13">
         <v>66.707364978807405</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="13">
         <v>277.29233437135599</v>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="13">
         <v>79.702665444735899</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="1">
         <v>5278</v>
       </c>
       <c r="E5" s="1">
         <v>1144</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
     </row>
     <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>13</v>
+      <c r="A6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="D6" s="2">
         <v>3048</v>
@@ -837,83 +837,83 @@
       <c r="E6" s="2">
         <v>572</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="9">
         <v>1964</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="9">
         <v>4854</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="15">
         <v>293.64031363021701</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="15">
         <v>88.213477624855599</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="15">
         <v>25.225352929200501</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="15">
         <v>194.65520854442201</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="15">
         <v>174.24312757275999</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="15">
         <v>276.24862320352401</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="15">
         <v>276.356686742102</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="15">
         <v>54.652194491503202</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="15">
         <v>219.427357240562</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="15">
         <v>173.55698442818701</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="15">
         <v>91.423507451253002</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="15">
         <v>96.357166141414297</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="2">
         <v>3046</v>
       </c>
       <c r="E7" s="2">
         <v>514</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
     </row>
     <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>14</v>
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D8" s="1">
         <v>1988</v>
@@ -921,94 +921,101 @@
       <c r="E8" s="1">
         <v>336</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>1964</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>2919</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="13">
         <v>312.62246587997799</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="13">
         <v>124.699621078633</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="13">
         <v>34.3941662806902</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="13">
         <v>90.046210117324094</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="13">
         <v>112.23896568156199</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="13">
         <v>512.98092271818405</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="13">
         <v>120.894265035811</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="13">
         <v>144.502569223573</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="13">
         <v>190.49328006180701</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="13">
         <v>86.398803966984701</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="13">
         <v>158.570346284219</v>
       </c>
-      <c r="S8" s="7">
+      <c r="S8" s="13">
         <v>76.158383671233395</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="1">
         <v>2342</v>
       </c>
       <c r="E9" s="1">
         <v>326</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -1025,31 +1032,24 @@
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
